--- a/Vf/TABLE_4_5/Table_5_PanelC_Multiplicative_MIDAS.xlsx
+++ b/Vf/TABLE_4_5/Table_5_PanelC_Multiplicative_MIDAS.xlsx
@@ -447,16 +447,16 @@
         <v>-0.9</v>
       </c>
       <c r="B2" t="n">
-        <v>1.126754108531721</v>
+        <v>1.126363966603823</v>
       </c>
       <c r="C2" t="n">
-        <v>1.127217719998808</v>
+        <v>1.126194662699311</v>
       </c>
       <c r="D2" t="n">
-        <v>1.110844048707709</v>
+        <v>1.110169125061643</v>
       </c>
       <c r="E2" t="n">
-        <v>1.128144540717726</v>
+        <v>1.127967381638924</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>-0.5</v>
       </c>
       <c r="B3" t="n">
-        <v>1.102157488093559</v>
+        <v>1.101889558749724</v>
       </c>
       <c r="C3" t="n">
-        <v>1.131713018127746</v>
+        <v>1.131688951509041</v>
       </c>
       <c r="D3" t="n">
-        <v>1.144746835157456</v>
+        <v>1.145007000966357</v>
       </c>
       <c r="E3" t="n">
-        <v>1.165125822757747</v>
+        <v>1.165289619638772</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1.100785055980052</v>
+        <v>1.100821324128619</v>
       </c>
       <c r="C4" t="n">
-        <v>1.134229035816607</v>
+        <v>1.134053028633255</v>
       </c>
       <c r="D4" t="n">
-        <v>1.14992279958566</v>
+        <v>1.149683483364637</v>
       </c>
       <c r="E4" t="n">
-        <v>1.159423341113643</v>
+        <v>1.159329449117814</v>
       </c>
     </row>
     <row r="5">
@@ -501,13 +501,13 @@
         <v>1.096547957448777</v>
       </c>
       <c r="C5" t="n">
-        <v>1.13990229361221</v>
+        <v>1.139498910615209</v>
       </c>
       <c r="D5" t="n">
-        <v>1.143754963628288</v>
+        <v>1.143458268031378</v>
       </c>
       <c r="E5" t="n">
-        <v>1.154585422496159</v>
+        <v>1.154463951141233</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>0.95</v>
       </c>
       <c r="B6" t="n">
-        <v>1.142275731783936</v>
+        <v>1.138788564248178</v>
       </c>
       <c r="C6" t="n">
-        <v>1.194081240882344</v>
+        <v>1.189377993005432</v>
       </c>
       <c r="D6" t="n">
-        <v>1.20260454647851</v>
+        <v>1.201242176425993</v>
       </c>
       <c r="E6" t="n">
-        <v>1.195095812970976</v>
+        <v>1.193904316937425</v>
       </c>
     </row>
   </sheetData>
